--- a/data/ground_truth/span_09_ground_truth.xlsx
+++ b/data/ground_truth/span_09_ground_truth.xlsx
@@ -478,6 +478,11 @@
       <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
       <c r="C5" t="inlineStr">
         <is>
           <t>20</t>
@@ -495,6 +500,11 @@
       </c>
     </row>
     <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Inventory</t>
+        </is>
+      </c>
       <c r="C6" t="inlineStr">
         <is>
           <t>12</t>
@@ -522,6 +532,11 @@
       <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Property</t>
+        </is>
+      </c>
       <c r="C8" t="inlineStr">
         <is>
           <t>90</t>
@@ -554,6 +569,11 @@
       <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Payables</t>
+        </is>
+      </c>
       <c r="C10" t="inlineStr">
         <is>
           <t>22</t>
@@ -571,15 +591,12 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="6">
     <mergeCell ref="A1:A3"/>
-    <mergeCell ref="B9:B10"/>
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="D2:E2"/>
-    <mergeCell ref="B4:B6"/>
     <mergeCell ref="A9:A10"/>
-    <mergeCell ref="B7:B8"/>
     <mergeCell ref="A4:A8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
